--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133850747</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133851031</v>
       </c>
       <c r="B4" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133850716</v>
+        <v>133850728</v>
       </c>
       <c r="B6" t="n">
-        <v>5199</v>
+        <v>83318</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622794</v>
+        <v>622608</v>
       </c>
       <c r="R6" t="n">
-        <v>7089534</v>
+        <v>7089213</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-106</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-95</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,32 +1181,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133850728</v>
+        <v>133850716</v>
       </c>
       <c r="B7" t="n">
-        <v>83316</v>
+        <v>5199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622608</v>
+        <v>622794</v>
       </c>
       <c r="R7" t="n">
-        <v>7089213</v>
+        <v>7089534</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-95</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-106</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133851074</v>
+        <v>133850748</v>
       </c>
       <c r="B8" t="n">
-        <v>83182</v>
+        <v>91889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622776</v>
+        <v>622742</v>
       </c>
       <c r="R8" t="n">
-        <v>7089508</v>
+        <v>7089561</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,32 +1385,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133850748</v>
+        <v>133851074</v>
       </c>
       <c r="B9" t="n">
-        <v>91883</v>
+        <v>83182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622742</v>
+        <v>622776</v>
       </c>
       <c r="R9" t="n">
-        <v>7089561</v>
+        <v>7089508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,7 +1592,7 @@
         <v>133850783</v>
       </c>
       <c r="B11" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133850729</v>
+        <v>133851073</v>
       </c>
       <c r="B12" t="n">
-        <v>83316</v>
+        <v>83182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622782</v>
+        <v>622611</v>
       </c>
       <c r="R12" t="n">
-        <v>7089524</v>
+        <v>7089212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1793,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133851030</v>
+        <v>133850729</v>
       </c>
       <c r="B13" t="n">
-        <v>91940</v>
+        <v>83318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,19 +1804,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1824,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622740</v>
+        <v>622782</v>
       </c>
       <c r="R13" t="n">
-        <v>7089312</v>
+        <v>7089524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,7 +1868,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133851073</v>
+        <v>133851030</v>
       </c>
       <c r="B14" t="n">
-        <v>83182</v>
+        <v>91946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,23 +1906,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622611</v>
+        <v>622740</v>
       </c>
       <c r="R14" t="n">
-        <v>7089212</v>
+        <v>7089312</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,7 +1996,7 @@
         <v>133850769</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>133850779</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>133850723</v>
       </c>
       <c r="B17" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>133850998</v>
       </c>
       <c r="B18" t="n">
-        <v>91916</v>
+        <v>91922</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133850780</v>
       </c>
       <c r="B19" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>133850782</v>
       </c>
       <c r="B20" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133850747</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133851031</v>
       </c>
       <c r="B4" t="n">
-        <v>91946</v>
+        <v>91948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>133850728</v>
       </c>
       <c r="B6" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133850748</v>
+        <v>133851074</v>
       </c>
       <c r="B8" t="n">
-        <v>91889</v>
+        <v>83183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622742</v>
+        <v>622776</v>
       </c>
       <c r="R8" t="n">
-        <v>7089561</v>
+        <v>7089508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,32 +1385,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133851074</v>
+        <v>133850748</v>
       </c>
       <c r="B9" t="n">
-        <v>83182</v>
+        <v>91891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622776</v>
+        <v>622742</v>
       </c>
       <c r="R9" t="n">
-        <v>7089508</v>
+        <v>7089561</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,7 +1592,7 @@
         <v>133850783</v>
       </c>
       <c r="B11" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>133851073</v>
       </c>
       <c r="B12" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>133850729</v>
       </c>
       <c r="B13" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>133851030</v>
       </c>
       <c r="B14" t="n">
-        <v>91946</v>
+        <v>91948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>133850769</v>
       </c>
       <c r="B15" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>133850779</v>
       </c>
       <c r="B16" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>133850723</v>
       </c>
       <c r="B17" t="n">
-        <v>91848</v>
+        <v>91850</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>133850998</v>
       </c>
       <c r="B18" t="n">
-        <v>91922</v>
+        <v>91924</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133850780</v>
       </c>
       <c r="B19" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>133850782</v>
       </c>
       <c r="B20" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133850747</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851059</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133851031</v>
       </c>
       <c r="B4" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850941</v>
       </c>
       <c r="B5" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133850728</v>
+        <v>133850716</v>
       </c>
       <c r="B6" t="n">
-        <v>83319</v>
+        <v>5201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622608</v>
+        <v>622794</v>
       </c>
       <c r="R6" t="n">
-        <v>7089213</v>
+        <v>7089534</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-95</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-106</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,32 +1181,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133850716</v>
+        <v>133850728</v>
       </c>
       <c r="B7" t="n">
-        <v>5199</v>
+        <v>83333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622794</v>
+        <v>622608</v>
       </c>
       <c r="R7" t="n">
-        <v>7089534</v>
+        <v>7089213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-106</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-95</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,7 +1286,7 @@
         <v>133851074</v>
       </c>
       <c r="B8" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>133850748</v>
       </c>
       <c r="B9" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>133851121</v>
       </c>
       <c r="B10" t="n">
-        <v>8444</v>
+        <v>8449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133850783</v>
       </c>
       <c r="B11" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133851073</v>
+        <v>133850729</v>
       </c>
       <c r="B12" t="n">
-        <v>83183</v>
+        <v>83333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622611</v>
+        <v>622782</v>
       </c>
       <c r="R12" t="n">
-        <v>7089212</v>
+        <v>7089524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1793,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133850729</v>
+        <v>133851073</v>
       </c>
       <c r="B13" t="n">
-        <v>83319</v>
+        <v>83197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,21 +1804,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622782</v>
+        <v>622611</v>
       </c>
       <c r="R13" t="n">
-        <v>7089524</v>
+        <v>7089212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,7 +1898,7 @@
         <v>133851030</v>
       </c>
       <c r="B14" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>133850769</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>133850779</v>
       </c>
       <c r="B16" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133850723</v>
+        <v>133850998</v>
       </c>
       <c r="B17" t="n">
-        <v>91850</v>
+        <v>91943</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2208,21 +2208,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622733</v>
+        <v>622559</v>
       </c>
       <c r="R17" t="n">
-        <v>7089490</v>
+        <v>7089347</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-100</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133850998</v>
+        <v>133850723</v>
       </c>
       <c r="B18" t="n">
-        <v>91924</v>
+        <v>91869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622559</v>
+        <v>622733</v>
       </c>
       <c r="R18" t="n">
-        <v>7089347</v>
+        <v>7089490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-100</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,7 +2404,7 @@
         <v>133850780</v>
       </c>
       <c r="B19" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>133850782</v>
       </c>
       <c r="B20" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133850729</v>
+        <v>133851030</v>
       </c>
       <c r="B12" t="n">
-        <v>83333</v>
+        <v>91967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,23 +1702,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1726,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622782</v>
+        <v>622740</v>
       </c>
       <c r="R12" t="n">
-        <v>7089524</v>
+        <v>7089312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,7 +1762,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133851030</v>
+        <v>133850729</v>
       </c>
       <c r="B14" t="n">
-        <v>91967</v>
+        <v>83333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,19 +1902,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622740</v>
+        <v>622782</v>
       </c>
       <c r="R14" t="n">
-        <v>7089312</v>
+        <v>7089524</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133850747</v>
       </c>
       <c r="B2" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851059</v>
       </c>
       <c r="B3" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133851031</v>
       </c>
       <c r="B4" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850941</v>
       </c>
       <c r="B5" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>133850728</v>
       </c>
       <c r="B7" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>133851074</v>
       </c>
       <c r="B8" t="n">
-        <v>83197</v>
+        <v>83207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>133850748</v>
       </c>
       <c r="B9" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133850783</v>
       </c>
       <c r="B11" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133851030</v>
+        <v>133850729</v>
       </c>
       <c r="B12" t="n">
-        <v>91967</v>
+        <v>83343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,19 +1702,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1722,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622740</v>
+        <v>622782</v>
       </c>
       <c r="R12" t="n">
-        <v>7089312</v>
+        <v>7089524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1766,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133851073</v>
+        <v>133851030</v>
       </c>
       <c r="B13" t="n">
-        <v>83197</v>
+        <v>91977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,23 +1804,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622611</v>
+        <v>622740</v>
       </c>
       <c r="R13" t="n">
-        <v>7089212</v>
+        <v>7089312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133850729</v>
+        <v>133851073</v>
       </c>
       <c r="B14" t="n">
-        <v>83333</v>
+        <v>83207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622782</v>
+        <v>622611</v>
       </c>
       <c r="R14" t="n">
-        <v>7089524</v>
+        <v>7089212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,7 +1996,7 @@
         <v>133850769</v>
       </c>
       <c r="B15" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>133850779</v>
       </c>
       <c r="B16" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133850998</v>
+        <v>133850723</v>
       </c>
       <c r="B17" t="n">
-        <v>91943</v>
+        <v>91879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2208,21 +2208,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>3242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622559</v>
+        <v>622733</v>
       </c>
       <c r="R17" t="n">
-        <v>7089347</v>
+        <v>7089490</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-100</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133850723</v>
+        <v>133850998</v>
       </c>
       <c r="B18" t="n">
-        <v>91869</v>
+        <v>91953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3242</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622733</v>
+        <v>622559</v>
       </c>
       <c r="R18" t="n">
-        <v>7089490</v>
+        <v>7089347</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-100</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,7 +2404,7 @@
         <v>133850780</v>
       </c>
       <c r="B19" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>133850782</v>
       </c>
       <c r="B20" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133851074</v>
+        <v>133850748</v>
       </c>
       <c r="B8" t="n">
-        <v>83207</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622776</v>
+        <v>622742</v>
       </c>
       <c r="R8" t="n">
-        <v>7089508</v>
+        <v>7089561</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,32 +1385,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133850748</v>
+        <v>133851074</v>
       </c>
       <c r="B9" t="n">
-        <v>91920</v>
+        <v>83207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622742</v>
+        <v>622776</v>
       </c>
       <c r="R9" t="n">
-        <v>7089561</v>
+        <v>7089508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133850748</v>
+        <v>133851074</v>
       </c>
       <c r="B8" t="n">
-        <v>91920</v>
+        <v>83207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622742</v>
+        <v>622776</v>
       </c>
       <c r="R8" t="n">
-        <v>7089561</v>
+        <v>7089508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,32 +1385,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133851074</v>
+        <v>133850748</v>
       </c>
       <c r="B9" t="n">
-        <v>83207</v>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622776</v>
+        <v>622742</v>
       </c>
       <c r="R9" t="n">
-        <v>7089508</v>
+        <v>7089561</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133850729</v>
+        <v>133851030</v>
       </c>
       <c r="B12" t="n">
-        <v>83343</v>
+        <v>91977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,23 +1702,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1726,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622782</v>
+        <v>622740</v>
       </c>
       <c r="R12" t="n">
-        <v>7089524</v>
+        <v>7089312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,7 +1762,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1793,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133851030</v>
+        <v>133851073</v>
       </c>
       <c r="B13" t="n">
-        <v>91977</v>
+        <v>83207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,19 +1800,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622740</v>
+        <v>622611</v>
       </c>
       <c r="R13" t="n">
-        <v>7089312</v>
+        <v>7089212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133851073</v>
+        <v>133850729</v>
       </c>
       <c r="B14" t="n">
-        <v>83207</v>
+        <v>83343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622611</v>
+        <v>622782</v>
       </c>
       <c r="R14" t="n">
-        <v>7089212</v>
+        <v>7089524</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133851030</v>
+        <v>133850729</v>
       </c>
       <c r="B12" t="n">
-        <v>91977</v>
+        <v>83343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,19 +1702,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1722,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622740</v>
+        <v>622782</v>
       </c>
       <c r="R12" t="n">
-        <v>7089312</v>
+        <v>7089524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1766,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133851073</v>
+        <v>133851030</v>
       </c>
       <c r="B13" t="n">
-        <v>83207</v>
+        <v>91977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,23 +1804,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622611</v>
+        <v>622740</v>
       </c>
       <c r="R13" t="n">
-        <v>7089212</v>
+        <v>7089312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133850729</v>
+        <v>133851073</v>
       </c>
       <c r="B14" t="n">
-        <v>83343</v>
+        <v>83207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622782</v>
+        <v>622611</v>
       </c>
       <c r="R14" t="n">
-        <v>7089524</v>
+        <v>7089212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133850747</v>
       </c>
       <c r="B2" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851059</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133851031</v>
       </c>
       <c r="B4" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850941</v>
       </c>
       <c r="B5" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>133850728</v>
       </c>
       <c r="B7" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>133851074</v>
       </c>
       <c r="B8" t="n">
-        <v>83207</v>
+        <v>83208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>133850748</v>
       </c>
       <c r="B9" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133850783</v>
       </c>
       <c r="B11" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>133850729</v>
       </c>
       <c r="B12" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133851030</v>
+        <v>133851073</v>
       </c>
       <c r="B13" t="n">
-        <v>91977</v>
+        <v>83208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,19 +1804,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1824,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622740</v>
+        <v>622611</v>
       </c>
       <c r="R13" t="n">
-        <v>7089312</v>
+        <v>7089212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,7 +1868,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133851073</v>
+        <v>133851030</v>
       </c>
       <c r="B14" t="n">
-        <v>83207</v>
+        <v>91979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,23 +1906,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622611</v>
+        <v>622740</v>
       </c>
       <c r="R14" t="n">
-        <v>7089212</v>
+        <v>7089312</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,7 +1996,7 @@
         <v>133850769</v>
       </c>
       <c r="B15" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>133850779</v>
       </c>
       <c r="B16" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>133850723</v>
       </c>
       <c r="B17" t="n">
-        <v>91879</v>
+        <v>91881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>133850998</v>
       </c>
       <c r="B18" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133850780</v>
       </c>
       <c r="B19" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>133850782</v>
       </c>
       <c r="B20" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133851074</v>
+        <v>133850748</v>
       </c>
       <c r="B8" t="n">
-        <v>83208</v>
+        <v>91922</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622776</v>
+        <v>622742</v>
       </c>
       <c r="R8" t="n">
-        <v>7089508</v>
+        <v>7089561</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,32 +1385,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133850748</v>
+        <v>133851074</v>
       </c>
       <c r="B9" t="n">
-        <v>91922</v>
+        <v>83208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622742</v>
+        <v>622776</v>
       </c>
       <c r="R9" t="n">
-        <v>7089561</v>
+        <v>7089508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133850729</v>
+        <v>133851030</v>
       </c>
       <c r="B12" t="n">
-        <v>83344</v>
+        <v>91979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,23 +1702,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1726,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622782</v>
+        <v>622740</v>
       </c>
       <c r="R12" t="n">
-        <v>7089524</v>
+        <v>7089312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,7 +1762,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133851030</v>
+        <v>133850729</v>
       </c>
       <c r="B14" t="n">
-        <v>91979</v>
+        <v>83344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,19 +1902,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622740</v>
+        <v>622782</v>
       </c>
       <c r="R14" t="n">
-        <v>7089312</v>
+        <v>7089524</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133850723</v>
+        <v>133850998</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>91955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2208,21 +2208,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622733</v>
+        <v>622559</v>
       </c>
       <c r="R17" t="n">
-        <v>7089490</v>
+        <v>7089347</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-100</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133850998</v>
+        <v>133850723</v>
       </c>
       <c r="B18" t="n">
-        <v>91955</v>
+        <v>91881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622559</v>
+        <v>622733</v>
       </c>
       <c r="R18" t="n">
-        <v>7089347</v>
+        <v>7089490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-100</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133851074</v>
+        <v>133850748</v>
       </c>
       <c r="B8" t="n">
-        <v>83208</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622776</v>
+        <v>622742</v>
       </c>
       <c r="R8" t="n">
-        <v>7089508</v>
+        <v>7089561</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,32 +1385,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133850748</v>
+        <v>133851074</v>
       </c>
       <c r="B9" t="n">
-        <v>91923</v>
+        <v>83208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622742</v>
+        <v>622776</v>
       </c>
       <c r="R9" t="n">
-        <v>7089561</v>
+        <v>7089508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133850747</v>
       </c>
       <c r="B2" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851059</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133851031</v>
       </c>
       <c r="B4" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850941</v>
       </c>
       <c r="B5" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>133850728</v>
       </c>
       <c r="B7" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133850748</v>
+        <v>133851074</v>
       </c>
       <c r="B8" t="n">
-        <v>91923</v>
+        <v>83215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622742</v>
+        <v>622776</v>
       </c>
       <c r="R8" t="n">
-        <v>7089561</v>
+        <v>7089508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,32 +1385,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133851074</v>
+        <v>133850748</v>
       </c>
       <c r="B9" t="n">
-        <v>83208</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622776</v>
+        <v>622742</v>
       </c>
       <c r="R9" t="n">
-        <v>7089508</v>
+        <v>7089561</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,7 +1592,7 @@
         <v>133850783</v>
       </c>
       <c r="B11" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133850729</v>
+        <v>133851030</v>
       </c>
       <c r="B12" t="n">
-        <v>83344</v>
+        <v>91987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,23 +1702,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1726,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622782</v>
+        <v>622740</v>
       </c>
       <c r="R12" t="n">
-        <v>7089524</v>
+        <v>7089312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,7 +1762,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1793,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133851030</v>
+        <v>133851073</v>
       </c>
       <c r="B13" t="n">
-        <v>91980</v>
+        <v>83215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,19 +1800,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622740</v>
+        <v>622611</v>
       </c>
       <c r="R13" t="n">
-        <v>7089312</v>
+        <v>7089212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133851073</v>
+        <v>133850729</v>
       </c>
       <c r="B14" t="n">
-        <v>83208</v>
+        <v>83351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622611</v>
+        <v>622782</v>
       </c>
       <c r="R14" t="n">
-        <v>7089212</v>
+        <v>7089524</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,7 +1996,7 @@
         <v>133850769</v>
       </c>
       <c r="B15" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>133850779</v>
       </c>
       <c r="B16" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>133850723</v>
       </c>
       <c r="B17" t="n">
-        <v>91882</v>
+        <v>91889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>133850998</v>
       </c>
       <c r="B18" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133850780</v>
       </c>
       <c r="B19" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>133850782</v>
       </c>
       <c r="B20" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133850747</v>
+        <v>133850998</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622730</v>
+        <v>622559</v>
       </c>
       <c r="R2" t="n">
-        <v>7089509</v>
+        <v>7089347</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-76</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133851059</v>
+        <v>133850769</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622794</v>
+        <v>622736</v>
       </c>
       <c r="R3" t="n">
-        <v>7089534</v>
+        <v>7089544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-85</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133851031</v>
+        <v>133850779</v>
       </c>
       <c r="B4" t="n">
-        <v>91987</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622520</v>
+        <v>622751</v>
       </c>
       <c r="R4" t="n">
-        <v>7089315</v>
+        <v>7089342</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-43</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133850941</v>
+        <v>133850780</v>
       </c>
       <c r="B5" t="n">
-        <v>80481</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1012,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622762</v>
+        <v>622668</v>
       </c>
       <c r="R5" t="n">
-        <v>7089540</v>
+        <v>7089299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-36</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,32 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133850716</v>
+        <v>133850782</v>
       </c>
       <c r="B6" t="n">
-        <v>5201</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622794</v>
+        <v>622672</v>
       </c>
       <c r="R6" t="n">
-        <v>7089534</v>
+        <v>7089459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-106</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133850728</v>
+        <v>133850783</v>
       </c>
       <c r="B7" t="n">
-        <v>83351</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1216,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622608</v>
+        <v>622776</v>
       </c>
       <c r="R7" t="n">
-        <v>7089213</v>
+        <v>7089513</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-95</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133851074</v>
+        <v>133851073</v>
       </c>
       <c r="B8" t="n">
-        <v>83215</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622776</v>
+        <v>622611</v>
       </c>
       <c r="R8" t="n">
-        <v>7089508</v>
+        <v>7089212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,32 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133850748</v>
+        <v>133851074</v>
       </c>
       <c r="B9" t="n">
-        <v>91930</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1420,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622742</v>
+        <v>622776</v>
       </c>
       <c r="R9" t="n">
-        <v>7089561</v>
+        <v>7089508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-71</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133851121</v>
+        <v>133850723</v>
       </c>
       <c r="B10" t="n">
-        <v>8449</v>
+        <v>91896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622541</v>
+        <v>622733</v>
       </c>
       <c r="R10" t="n">
-        <v>7089335</v>
+        <v>7089490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-100</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,32 +1593,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133850783</v>
+        <v>133850747</v>
       </c>
       <c r="B11" t="n">
-        <v>91967</v>
+        <v>91937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622776</v>
+        <v>622730</v>
       </c>
       <c r="R11" t="n">
-        <v>7089513</v>
+        <v>7089509</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,7 +1668,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-47</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-76</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1691,30 +1695,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133851030</v>
+        <v>133850748</v>
       </c>
       <c r="B12" t="n">
-        <v>91987</v>
+        <v>91937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1722,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622740</v>
+        <v>622742</v>
       </c>
       <c r="R12" t="n">
-        <v>7089312</v>
+        <v>7089561</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133851073</v>
+        <v>133851059</v>
       </c>
       <c r="B13" t="n">
-        <v>83215</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1824,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622611</v>
+        <v>622794</v>
       </c>
       <c r="R13" t="n">
-        <v>7089212</v>
+        <v>7089534</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,7 +1872,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-85</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133850729</v>
+        <v>133850728</v>
       </c>
       <c r="B14" t="n">
-        <v>83351</v>
+        <v>83358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622782</v>
+        <v>622608</v>
       </c>
       <c r="R14" t="n">
-        <v>7089524</v>
+        <v>7089213</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1974,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-95</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1993,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133850769</v>
+        <v>133850729</v>
       </c>
       <c r="B15" t="n">
-        <v>91967</v>
+        <v>83358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,21 +2012,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622736</v>
+        <v>622782</v>
       </c>
       <c r="R15" t="n">
-        <v>7089544</v>
+        <v>7089524</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-57</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-94</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133850779</v>
+        <v>133850941</v>
       </c>
       <c r="B16" t="n">
-        <v>91967</v>
+        <v>80488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2106,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2130,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622751</v>
+        <v>622762</v>
       </c>
       <c r="R16" t="n">
-        <v>7089342</v>
+        <v>7089540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2170,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-50</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2197,32 +2205,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133850723</v>
+        <v>133850716</v>
       </c>
       <c r="B17" t="n">
-        <v>91889</v>
+        <v>5201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622733</v>
+        <v>622794</v>
       </c>
       <c r="R17" t="n">
-        <v>7089490</v>
+        <v>7089534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-100</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-106</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2299,32 +2307,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133850998</v>
+        <v>133851121</v>
       </c>
       <c r="B18" t="n">
-        <v>91963</v>
+        <v>8449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2334,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622559</v>
+        <v>622541</v>
       </c>
       <c r="R18" t="n">
-        <v>7089347</v>
+        <v>7089335</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-72</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2401,32 +2409,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133850780</v>
+        <v>133850816</v>
       </c>
       <c r="B19" t="n">
-        <v>91967</v>
+        <v>103907</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>223284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2436,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622668</v>
+        <v>622809</v>
       </c>
       <c r="R19" t="n">
-        <v>7089299</v>
+        <v>7089536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,7 +2484,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-49</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-65</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2500,108 +2508,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>133850782</v>
-      </c>
-      <c r="B20" t="n">
-        <v>91967</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Skogen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>622672</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7089459</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-48</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22550-2022 artfynd.xlsx
+++ b/artfynd/A 22550-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850998</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850769</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850779</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850780</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850782</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850783</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851073</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851074</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850723</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850747</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850748</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851059</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850728</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850729</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850941</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850716</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851121</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,8 +2598,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850816</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>